--- a/notebooks/extra_tables/ema_rwd_final_statistics_tables_logit_without_outliers_formated.xlsx
+++ b/notebooks/extra_tables/ema_rwd_final_statistics_tables_logit_without_outliers_formated.xlsx
@@ -587,7 +587,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Study required by a Risk Management Plan</t>
+          <t>Study required by an RMP</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
